--- a/data/Tables/ID_to_create.xlsx
+++ b/data/Tables/ID_to_create.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/canada_metal_sustainability_db/data/Tables/IDs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{902D2D5E-118C-4B1A-80C4-DB114FFE0738}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{771B9936-0657-4B79-BF4A-95D67154F162}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="companies" sheetId="4" r:id="rId1"/>
@@ -2599,12 +2599,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -2643,7 +2649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2657,6 +2663,8 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2942,17 +2950,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE2B370-F97A-46D7-85D8-F18D421C8C1C}">
   <dimension ref="A1:F271"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.44140625" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>826</v>
       </c>
@@ -2972,7 +2980,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2989,7 +2997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3006,7 +3014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3023,7 +3031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3040,7 +3048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3057,7 +3065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3074,7 +3082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3091,7 +3099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3108,7 +3116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3125,7 +3133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3142,7 +3150,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3159,7 +3167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3176,7 +3184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -3193,7 +3201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -3210,7 +3218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -3227,7 +3235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -3244,7 +3252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -3261,7 +3269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -3278,7 +3286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -3295,7 +3303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -3312,7 +3320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>838</v>
       </c>
@@ -3329,7 +3337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>838</v>
       </c>
@@ -3346,7 +3354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -3363,7 +3371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -3380,7 +3388,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -3397,7 +3405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -3414,7 +3422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -3431,7 +3439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -3448,7 +3456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>65</v>
       </c>
@@ -3465,7 +3473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>81</v>
       </c>
@@ -3482,7 +3490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>838</v>
       </c>
@@ -3499,7 +3507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -3516,7 +3524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>92</v>
       </c>
@@ -3533,7 +3541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>92</v>
       </c>
@@ -3550,7 +3558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>838</v>
       </c>
@@ -3567,7 +3575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>98</v>
       </c>
@@ -3584,7 +3592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -3601,7 +3609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>838</v>
       </c>
@@ -3618,7 +3626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>838</v>
       </c>
@@ -3635,7 +3643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -3652,7 +3660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>838</v>
       </c>
@@ -3669,7 +3677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -3686,7 +3694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>119</v>
       </c>
@@ -3703,7 +3711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>119</v>
       </c>
@@ -3720,7 +3728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>119</v>
       </c>
@@ -3737,7 +3745,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>119</v>
       </c>
@@ -3754,7 +3762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>838</v>
       </c>
@@ -3771,7 +3779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>838</v>
       </c>
@@ -3788,7 +3796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>838</v>
       </c>
@@ -3805,7 +3813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>838</v>
       </c>
@@ -3822,7 +3830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>838</v>
       </c>
@@ -3839,7 +3847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>146</v>
       </c>
@@ -3856,7 +3864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>838</v>
       </c>
@@ -3873,7 +3881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>153</v>
       </c>
@@ -3890,7 +3898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>153</v>
       </c>
@@ -3907,7 +3915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>159</v>
       </c>
@@ -3924,7 +3932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>838</v>
       </c>
@@ -3941,7 +3949,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>166</v>
       </c>
@@ -3958,7 +3966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>170</v>
       </c>
@@ -3975,7 +3983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>33</v>
       </c>
@@ -3992,7 +4000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -4009,7 +4017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>180</v>
       </c>
@@ -4026,7 +4034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>183</v>
       </c>
@@ -4043,7 +4051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>186</v>
       </c>
@@ -4060,7 +4068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>190</v>
       </c>
@@ -4077,7 +4085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>194</v>
       </c>
@@ -4094,7 +4102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>194</v>
       </c>
@@ -4111,7 +4119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>200</v>
       </c>
@@ -4128,7 +4136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>203</v>
       </c>
@@ -4145,7 +4153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>206</v>
       </c>
@@ -4162,7 +4170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>209</v>
       </c>
@@ -4179,7 +4187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>212</v>
       </c>
@@ -4196,7 +4204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>216</v>
       </c>
@@ -4213,7 +4221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>219</v>
       </c>
@@ -4230,7 +4238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>223</v>
       </c>
@@ -4247,7 +4255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>227</v>
       </c>
@@ -4264,7 +4272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>230</v>
       </c>
@@ -4281,7 +4289,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>230</v>
       </c>
@@ -4298,7 +4306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>236</v>
       </c>
@@ -4315,7 +4323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>236</v>
       </c>
@@ -4332,7 +4340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>242</v>
       </c>
@@ -4349,7 +4357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>246</v>
       </c>
@@ -4366,7 +4374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>250</v>
       </c>
@@ -4383,7 +4391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>254</v>
       </c>
@@ -4400,7 +4408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>258</v>
       </c>
@@ -4417,7 +4425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>261</v>
       </c>
@@ -4434,7 +4442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>261</v>
       </c>
@@ -4451,7 +4459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>266</v>
       </c>
@@ -4468,7 +4476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>270</v>
       </c>
@@ -4485,7 +4493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>274</v>
       </c>
@@ -4502,7 +4510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>278</v>
       </c>
@@ -4519,7 +4527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>281</v>
       </c>
@@ -4536,7 +4544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>285</v>
       </c>
@@ -4553,7 +4561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>285</v>
       </c>
@@ -4570,7 +4578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>285</v>
       </c>
@@ -4587,7 +4595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>285</v>
       </c>
@@ -4604,7 +4612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>285</v>
       </c>
@@ -4621,7 +4629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>298</v>
       </c>
@@ -4638,7 +4646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>298</v>
       </c>
@@ -4655,7 +4663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>298</v>
       </c>
@@ -4672,7 +4680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>298</v>
       </c>
@@ -4689,7 +4697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>298</v>
       </c>
@@ -4706,7 +4714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>298</v>
       </c>
@@ -4723,7 +4731,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>298</v>
       </c>
@@ -4740,7 +4748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>298</v>
       </c>
@@ -4757,7 +4765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>298</v>
       </c>
@@ -4774,7 +4782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>298</v>
       </c>
@@ -4791,7 +4799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>298</v>
       </c>
@@ -4808,7 +4816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>322</v>
       </c>
@@ -4825,7 +4833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>326</v>
       </c>
@@ -4842,7 +4850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>329</v>
       </c>
@@ -4859,7 +4867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>332</v>
       </c>
@@ -4876,7 +4884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>336</v>
       </c>
@@ -4893,7 +4901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>340</v>
       </c>
@@ -4910,7 +4918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>344</v>
       </c>
@@ -4927,7 +4935,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>344</v>
       </c>
@@ -4944,7 +4952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>344</v>
       </c>
@@ -4961,7 +4969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>351</v>
       </c>
@@ -4978,7 +4986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>354</v>
       </c>
@@ -4995,7 +5003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>354</v>
       </c>
@@ -5012,7 +5020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>354</v>
       </c>
@@ -5029,7 +5037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>354</v>
       </c>
@@ -5046,7 +5054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>354</v>
       </c>
@@ -5063,7 +5071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>354</v>
       </c>
@@ -5080,7 +5088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>354</v>
       </c>
@@ -5097,7 +5105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>354</v>
       </c>
@@ -5114,7 +5122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>354</v>
       </c>
@@ -5131,7 +5139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>374</v>
       </c>
@@ -5148,7 +5156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>377</v>
       </c>
@@ -5165,7 +5173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>381</v>
       </c>
@@ -5182,7 +5190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>384</v>
       </c>
@@ -5199,7 +5207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>387</v>
       </c>
@@ -5216,7 +5224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>391</v>
       </c>
@@ -5233,7 +5241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>391</v>
       </c>
@@ -5250,7 +5258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>397</v>
       </c>
@@ -5267,7 +5275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>401</v>
       </c>
@@ -5284,7 +5292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>404</v>
       </c>
@@ -5301,7 +5309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>408</v>
       </c>
@@ -5318,7 +5326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>411</v>
       </c>
@@ -5335,7 +5343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>415</v>
       </c>
@@ -5352,7 +5360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>418</v>
       </c>
@@ -5369,7 +5377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>421</v>
       </c>
@@ -5386,7 +5394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>425</v>
       </c>
@@ -5403,7 +5411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>425</v>
       </c>
@@ -5420,7 +5428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>431</v>
       </c>
@@ -5437,7 +5445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>434</v>
       </c>
@@ -5454,7 +5462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>437</v>
       </c>
@@ -5471,7 +5479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>441</v>
       </c>
@@ -5488,7 +5496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>445</v>
       </c>
@@ -5505,7 +5513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>449</v>
       </c>
@@ -5522,7 +5530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>453</v>
       </c>
@@ -5539,7 +5547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>456</v>
       </c>
@@ -5556,7 +5564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>460</v>
       </c>
@@ -5573,7 +5581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>464</v>
       </c>
@@ -5590,7 +5598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>468</v>
       </c>
@@ -5607,7 +5615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>471</v>
       </c>
@@ -5624,7 +5632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>471</v>
       </c>
@@ -5641,7 +5649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>476</v>
       </c>
@@ -5658,7 +5666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>476</v>
       </c>
@@ -5675,7 +5683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>482</v>
       </c>
@@ -5692,7 +5700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>486</v>
       </c>
@@ -5709,7 +5717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>486</v>
       </c>
@@ -5726,7 +5734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>492</v>
       </c>
@@ -5743,7 +5751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>492</v>
       </c>
@@ -5760,7 +5768,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>492</v>
       </c>
@@ -5777,7 +5785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>492</v>
       </c>
@@ -5794,7 +5802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>492</v>
       </c>
@@ -5811,7 +5819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>492</v>
       </c>
@@ -5828,7 +5836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>492</v>
       </c>
@@ -5845,7 +5853,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>492</v>
       </c>
@@ -5862,7 +5870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>492</v>
       </c>
@@ -5879,7 +5887,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>492</v>
       </c>
@@ -5896,7 +5904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>514</v>
       </c>
@@ -5913,7 +5921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>518</v>
       </c>
@@ -5930,7 +5938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>522</v>
       </c>
@@ -5947,7 +5955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>526</v>
       </c>
@@ -5964,7 +5972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>530</v>
       </c>
@@ -5981,7 +5989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>533</v>
       </c>
@@ -5998,7 +6006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>537</v>
       </c>
@@ -6015,7 +6023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>541</v>
       </c>
@@ -6032,7 +6040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>545</v>
       </c>
@@ -6049,7 +6057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>549</v>
       </c>
@@ -6066,7 +6074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>553</v>
       </c>
@@ -6083,7 +6091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>557</v>
       </c>
@@ -6100,7 +6108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>561</v>
       </c>
@@ -6117,7 +6125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>564</v>
       </c>
@@ -6134,7 +6142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>564</v>
       </c>
@@ -6151,7 +6159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>570</v>
       </c>
@@ -6168,7 +6176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>570</v>
       </c>
@@ -6185,7 +6193,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>570</v>
       </c>
@@ -6202,7 +6210,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>570</v>
       </c>
@@ -6219,7 +6227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>570</v>
       </c>
@@ -6236,7 +6244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>570</v>
       </c>
@@ -6253,7 +6261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>570</v>
       </c>
@@ -6270,7 +6278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>570</v>
       </c>
@@ -6287,7 +6295,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>570</v>
       </c>
@@ -6304,7 +6312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>570</v>
       </c>
@@ -6321,7 +6329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>570</v>
       </c>
@@ -6338,7 +6346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>570</v>
       </c>
@@ -6355,7 +6363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>598</v>
       </c>
@@ -6372,7 +6380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>602</v>
       </c>
@@ -6389,7 +6397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>606</v>
       </c>
@@ -6406,7 +6414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>610</v>
       </c>
@@ -6423,7 +6431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>613</v>
       </c>
@@ -6440,7 +6448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>616</v>
       </c>
@@ -6457,7 +6465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>619</v>
       </c>
@@ -6474,7 +6482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>623</v>
       </c>
@@ -6491,7 +6499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>627</v>
       </c>
@@ -6508,7 +6516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>627</v>
       </c>
@@ -6525,7 +6533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>633</v>
       </c>
@@ -6542,7 +6550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>637</v>
       </c>
@@ -6559,7 +6567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>641</v>
       </c>
@@ -6576,7 +6584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>645</v>
       </c>
@@ -6593,7 +6601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>649</v>
       </c>
@@ -6610,7 +6618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>652</v>
       </c>
@@ -6627,7 +6635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>655</v>
       </c>
@@ -6644,7 +6652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>658</v>
       </c>
@@ -6661,7 +6669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>658</v>
       </c>
@@ -6678,7 +6686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>664</v>
       </c>
@@ -6695,7 +6703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>667</v>
       </c>
@@ -6712,7 +6720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>667</v>
       </c>
@@ -6729,7 +6737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>673</v>
       </c>
@@ -6746,7 +6754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>676</v>
       </c>
@@ -6763,7 +6771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>676</v>
       </c>
@@ -6780,7 +6788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>681</v>
       </c>
@@ -6797,7 +6805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>685</v>
       </c>
@@ -6814,7 +6822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>689</v>
       </c>
@@ -6831,7 +6839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>692</v>
       </c>
@@ -6848,7 +6856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>692</v>
       </c>
@@ -6865,7 +6873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>698</v>
       </c>
@@ -6882,7 +6890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>702</v>
       </c>
@@ -6899,7 +6907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>702</v>
       </c>
@@ -6916,7 +6924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>702</v>
       </c>
@@ -6933,7 +6941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>709</v>
       </c>
@@ -6950,7 +6958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>709</v>
       </c>
@@ -6967,7 +6975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>714</v>
       </c>
@@ -6984,7 +6992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>714</v>
       </c>
@@ -7001,7 +7009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>714</v>
       </c>
@@ -7018,7 +7026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>721</v>
       </c>
@@ -7035,7 +7043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>725</v>
       </c>
@@ -7052,7 +7060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>728</v>
       </c>
@@ -7069,7 +7077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>732</v>
       </c>
@@ -7086,7 +7094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>735</v>
       </c>
@@ -7103,7 +7111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>738</v>
       </c>
@@ -7120,7 +7128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>741</v>
       </c>
@@ -7137,7 +7145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>745</v>
       </c>
@@ -7154,7 +7162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>745</v>
       </c>
@@ -7171,7 +7179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>745</v>
       </c>
@@ -7188,7 +7196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>745</v>
       </c>
@@ -7205,7 +7213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>745</v>
       </c>
@@ -7222,7 +7230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>745</v>
       </c>
@@ -7239,7 +7247,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>745</v>
       </c>
@@ -7256,7 +7264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>745</v>
       </c>
@@ -7273,7 +7281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>745</v>
       </c>
@@ -7290,7 +7298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>745</v>
       </c>
@@ -7307,7 +7315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>745</v>
       </c>
@@ -7324,7 +7332,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>769</v>
       </c>
@@ -7341,7 +7349,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>773</v>
       </c>
@@ -7358,7 +7366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>776</v>
       </c>
@@ -7375,7 +7383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>779</v>
       </c>
@@ -7392,7 +7400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>783</v>
       </c>
@@ -7409,7 +7417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>786</v>
       </c>
@@ -7426,7 +7434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>790</v>
       </c>
@@ -7443,7 +7451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>793</v>
       </c>
@@ -7460,7 +7468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>793</v>
       </c>
@@ -7477,7 +7485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>793</v>
       </c>
@@ -7494,7 +7502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>801</v>
       </c>
@@ -7511,7 +7519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>805</v>
       </c>
@@ -7528,7 +7536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>808</v>
       </c>
@@ -7545,7 +7553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>811</v>
       </c>
@@ -7570,16 +7578,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F5FA7-71F9-49C8-9BC8-0B44C1C55C1D}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>827</v>
       </c>
@@ -7599,43 +7608,49 @@
         <v>833</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>832</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>832</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
         <v>832</v>
@@ -7644,613 +7659,610 @@
         <v>834</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>299</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>301</v>
       </c>
       <c r="D5" t="s">
-        <v>832</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>299</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>309</v>
       </c>
       <c r="D6" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>832</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>709</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>710</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>711</v>
       </c>
       <c r="D9" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>709</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>712</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>713</v>
       </c>
       <c r="D10" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>299</v>
       </c>
       <c r="B11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C11" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D11" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>830</v>
+      </c>
+      <c r="F11" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>299</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C12" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D12" t="s">
         <v>830</v>
       </c>
-      <c r="F12" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="B13" t="s">
-        <v>308</v>
-      </c>
-      <c r="C13" t="s">
-        <v>309</v>
-      </c>
-      <c r="D13" t="s">
-        <v>302</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>299</v>
       </c>
       <c r="B14" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C14" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D14" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>299</v>
       </c>
       <c r="B15" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C15" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="D15" t="s">
         <v>830</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E15"/>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>299</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>305</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>321</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>355</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>362</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>367</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>355</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>366</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>363</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>355</v>
+        <v>492</v>
       </c>
       <c r="B20" t="s">
-        <v>360</v>
+        <v>493</v>
       </c>
       <c r="C20" t="s">
-        <v>361</v>
+        <v>508</v>
       </c>
       <c r="D20" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>492</v>
       </c>
       <c r="B21" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C21" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D21" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>492</v>
       </c>
       <c r="B22" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C22" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D22" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>492</v>
+        <v>587</v>
       </c>
       <c r="B23" t="s">
-        <v>503</v>
+        <v>590</v>
       </c>
       <c r="C23" t="s">
-        <v>498</v>
+        <v>589</v>
       </c>
       <c r="D23" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="B24" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="C24" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="D24" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="B25" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="C25" t="s">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="D25" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="B26" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="C26" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="D26" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>571</v>
       </c>
       <c r="B27" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C27" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D27" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>571</v>
       </c>
       <c r="B28" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C28" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D28" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>571</v>
       </c>
       <c r="B29" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C29" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D29" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>571</v>
       </c>
       <c r="B30" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C30" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D30" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="B31" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C31" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D31" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B32" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C32" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D32" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>587</v>
+        <v>659</v>
       </c>
       <c r="B33" t="s">
-        <v>594</v>
+        <v>660</v>
       </c>
       <c r="C33" t="s">
-        <v>595</v>
+        <v>661</v>
       </c>
       <c r="D33" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>587</v>
+        <v>659</v>
       </c>
       <c r="B34" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="C34" t="s">
-        <v>593</v>
+        <v>663</v>
       </c>
       <c r="D34" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>587</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s">
-        <v>596</v>
+        <v>362</v>
       </c>
       <c r="C35" t="s">
-        <v>597</v>
+        <v>367</v>
       </c>
       <c r="D35" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>659</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="C36" t="s">
-        <v>661</v>
+        <v>363</v>
       </c>
       <c r="D36" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>659</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s">
-        <v>662</v>
+        <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>663</v>
+        <v>361</v>
       </c>
       <c r="D37" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="B38" t="s">
-        <v>710</v>
+        <v>747</v>
       </c>
       <c r="C38" t="s">
-        <v>711</v>
+        <v>750</v>
       </c>
       <c r="D38" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="B39" t="s">
-        <v>712</v>
+        <v>749</v>
       </c>
       <c r="C39" t="s">
-        <v>713</v>
+        <v>755</v>
       </c>
       <c r="D39" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>746</v>
       </c>
       <c r="B40" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C40" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D40" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>746</v>
       </c>
       <c r="B41" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C41" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="D41" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>746</v>
       </c>
       <c r="B42" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C42" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D42" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>746</v>
       </c>
       <c r="B43" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C43" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="D43" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>746</v>
       </c>
       <c r="B44" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="C44" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D44" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>746</v>
+        <v>565</v>
       </c>
       <c r="B45" t="s">
-        <v>756</v>
+        <v>566</v>
       </c>
       <c r="C45" t="s">
-        <v>748</v>
+        <v>567</v>
       </c>
       <c r="D45" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>746</v>
+        <v>565</v>
       </c>
       <c r="B46" t="s">
-        <v>762</v>
+        <v>568</v>
       </c>
       <c r="C46" t="s">
-        <v>757</v>
+        <v>569</v>
       </c>
       <c r="D46" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{4E2F5FA7-71F9-49C8-9BC8-0B44C1C55C1D}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F49">
-      <sortCondition ref="A1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F46">
+      <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
